--- a/prc.xlsx
+++ b/prc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\Work\#Tasks\SCT-55562\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543C3EAC-A0A7-424B-9456-7BA5BB830EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388FD173-8EF9-4BEA-B23C-79892A370032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51585" yWindow="3990" windowWidth="2400" windowHeight="585" xr2:uid="{C0EF8FEF-6EA5-4AC1-93FF-DD82B4E03936}"/>
+    <workbookView xWindow="51480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C0EF8FEF-6EA5-4AC1-93FF-DD82B4E03936}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист2!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
   <si>
     <t>prc</t>
   </si>
@@ -291,13 +291,103 @@
   </si>
   <si>
     <t>LastWorkDate2</t>
+  </si>
+  <si>
+    <t>p_HO_603</t>
+  </si>
+  <si>
+    <t>p_HO_626</t>
+  </si>
+  <si>
+    <t>p_HO_637</t>
+  </si>
+  <si>
+    <t>p_HO_648</t>
+  </si>
+  <si>
+    <t>p_HO_649</t>
+  </si>
+  <si>
+    <t>p_HO_652</t>
+  </si>
+  <si>
+    <t>p_HO_668</t>
+  </si>
+  <si>
+    <t>p_HO_669</t>
+  </si>
+  <si>
+    <t>p_HO_706</t>
+  </si>
+  <si>
+    <t>p_HO_716_717</t>
+  </si>
+  <si>
+    <t>p_HO_736</t>
+  </si>
+  <si>
+    <t>p_HO_748</t>
+  </si>
+  <si>
+    <t>p_HO_749</t>
+  </si>
+  <si>
+    <t>p_HO_773</t>
+  </si>
+  <si>
+    <t>p_HO_863</t>
+  </si>
+  <si>
+    <t>p_HO_881</t>
+  </si>
+  <si>
+    <t>p_HO_885</t>
+  </si>
+  <si>
+    <t>p_HO_942</t>
+  </si>
+  <si>
+    <t>p_HO_943</t>
+  </si>
+  <si>
+    <t>p_HO_952</t>
+  </si>
+  <si>
+    <t>p_HO_954</t>
+  </si>
+  <si>
+    <t>StartHODate</t>
+  </si>
+  <si>
+    <t>StartHO668Date</t>
+  </si>
+  <si>
+    <t>Дата начала работы ХО 603, 626, 637, 648, 649, 652, 706, 716, 717, 736, 749, 773, 863, 881, 942, 943, 954</t>
+  </si>
+  <si>
+    <t>Дата начала работы ХО 668, 669</t>
+  </si>
+  <si>
+    <t>Наличие</t>
+  </si>
+  <si>
+    <t>Дата начала учёта классов паёв</t>
+  </si>
+  <si>
+    <t>ShareClassStartDate</t>
+  </si>
+  <si>
+    <t>Дата начала работы ХО 748, 885</t>
+  </si>
+  <si>
+    <t>StartHO748Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,8 +427,24 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,13 +453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,7 +476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -372,40 +484,198 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,616 +1023,616 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="4">
         <v>20200327</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="4">
         <v>20200330</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="4">
         <v>20200424</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="4">
         <v>20160101</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="4">
         <v>20160111</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="4">
         <v>20130408</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="4">
         <v>20150824</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="4">
         <v>20180101</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="4">
         <v>20230101</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="4">
         <v>20120801</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>20150101</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>20000101</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>20220715</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="A15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4">
         <v>20151231</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>20220419</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>20220201</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>20231231</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>20500101</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>20161231</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>20161231</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>20241231</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>20161231</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>20250101</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>20161231</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>20250101</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>20181028</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>20190410</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>20190401</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>20180401</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="4">
         <v>20210518</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>20230328</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="3">
         <v>3</v>
       </c>
     </row>
@@ -1379,51 +1649,389 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C828886-92BC-4B72-9160-0433DB06B04B}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="74.85546875" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="24">
+        <v>20161231</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="27"/>
+    </row>
+    <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="21">
+        <v>20170101</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="19"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="19"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="19"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="19"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="19"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="19"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="30">
+        <v>20181001</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="31"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="29"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="33">
+        <v>20260101</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{2C828886-92BC-4B72-9160-0433DB06B04B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F22">
+    <sortCondition ref="B1:B22"/>
+  </sortState>
+  <mergeCells count="15">
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="B4:B19"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="F2:F3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
